--- a/tame_output/ON/bt/strategyON_20240104.xlsx
+++ b/tame_output/ON/bt/strategyON_20240104.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.7%</t>
+          <t>131.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1831"/>
+  <dimension ref="A1:G1832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346936740543288</v>
+        <v>3.346417924612275</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43674,6 +43674,29 @@
       </c>
       <c r="G1831" t="n">
         <v>4.470388864684447</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="2" t="n">
+        <v>45294</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>3.300926710461961</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>3.130069279090508</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>1.592085525359104</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>3.766547064920402</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>2.233375965816716</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>4.470094858580538</v>
       </c>
     </row>
   </sheetData>
